--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02763968179925339</v>
+        <v>0.01628713796514822</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02763968179925339</v>
+        <v>0.01628713796514822</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01417956584676861</v>
+        <v>0.008564909239566073</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02713803617362584</v>
+        <v>0.01601188492398142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02713803617362584</v>
+        <v>0.01601188492398142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01500245891289306</v>
+        <v>0.008923534056332331</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02720532238784398</v>
+        <v>0.01604263048314328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02720532238784398</v>
+        <v>0.01604263048314328</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01449236093032022</v>
+        <v>0.008697372292551436</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02721269936732255</v>
+        <v>0.01602450712547577</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02721269936732255</v>
+        <v>0.01602450712547577</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01404198626302601</v>
+        <v>0.008470014949227037</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02695545547697991</v>
+        <v>0.01584298654529437</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02695545547697991</v>
+        <v>0.01584298654529437</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01364790941196322</v>
+        <v>0.008308435621212583</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02675229171562987</v>
+        <v>0.01569034612198242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02675229171562987</v>
+        <v>0.01569034612198242</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01325727631945278</v>
+        <v>0.008127654459172453</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02639271715395874</v>
+        <v>0.01544283810067519</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02639271715395874</v>
+        <v>0.01544283810067519</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01290112009197724</v>
+        <v>0.007968028915831597</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02600184344435978</v>
+        <v>0.01517638242271515</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02600184344435978</v>
+        <v>0.01517638242271515</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01255809751785537</v>
+        <v>0.00781979771350221</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02558858989877062</v>
+        <v>0.01489779720142817</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02558858989877062</v>
+        <v>0.01489779720142817</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01221952823732404</v>
+        <v>0.007677135983715958</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0251706683061594</v>
+        <v>0.01462072165497543</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0251706683061594</v>
+        <v>0.01462072165497543</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01186314847748673</v>
+        <v>0.007529096256140905</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02476952146314636</v>
+        <v>0.01435495618744069</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02476952146314636</v>
+        <v>0.01435495618744069</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01147657147397896</v>
+        <v>0.007368219948379666</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02440096830875906</v>
+        <v>0.01411438278605859</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02440096830875906</v>
+        <v>0.01411438278605859</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01105823866395064</v>
+        <v>0.007195353297021486</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0240792976666997</v>
+        <v>0.01390651634726437</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0240792976666997</v>
+        <v>0.01390651634726437</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01061077900198231</v>
+        <v>0.0070111119284322</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02380973519812932</v>
+        <v>0.01373440612341977</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02380973519812932</v>
+        <v>0.01373440612341977</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01013594869953874</v>
+        <v>0.006818284876716599</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02359496469468703</v>
+        <v>0.01359944442086142</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02359496469468703</v>
+        <v>0.01359944442086142</v>
       </c>
       <c r="D16" t="n">
-        <v>0.009631396462241768</v>
+        <v>0.006616241841186026</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02343895262307751</v>
+        <v>0.01350373743890074</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02343895262307751</v>
+        <v>0.01350373743890074</v>
       </c>
       <c r="D17" t="n">
-        <v>0.009110425503363736</v>
+        <v>0.006407460065520364</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02334909327364398</v>
+        <v>0.01345142839949767</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02334909327364398</v>
+        <v>0.01345142839949767</v>
       </c>
       <c r="D18" t="n">
-        <v>0.008577728450713033</v>
+        <v>0.006214353564186691</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02333452532446803</v>
+        <v>0.01344766360865208</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02333452532446803</v>
+        <v>0.01344766360865208</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008037988577238397</v>
+        <v>0.006013703946162912</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02340429703288307</v>
+        <v>0.01349752223000632</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02340429703288307</v>
+        <v>0.01349752223000632</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007514132443343848</v>
+        <v>0.00582803742946932</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02356424174863286</v>
+        <v>0.01360400433755551</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02356424174863286</v>
+        <v>0.01360400433755551</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007015514637354166</v>
+        <v>0.005669162563062705</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02382321168840165</v>
+        <v>0.01377226698520908</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02382321168840165</v>
+        <v>0.01377226698520908</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006552391259821969</v>
+        <v>0.005516370080292273</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02418451441024563</v>
+        <v>0.01400397360022844</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02418451441024563</v>
+        <v>0.01400397360022844</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006169849007546693</v>
+        <v>0.005417103821937067</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02465178941139275</v>
+        <v>0.01426574825912936</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02465178941139275</v>
+        <v>0.01426574825912936</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005874699092307031</v>
+        <v>0.005356902472700994</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0251524416764417</v>
+        <v>0.01461864079940425</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0251524416764417</v>
+        <v>0.01461864079940425</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00567177806069341</v>
+        <v>0.005332500331308992</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02583028328114063</v>
+        <v>0.01504442520899544</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02583028328114063</v>
+        <v>0.01504442520899544</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005542118035687733</v>
+        <v>0.005338586662651532</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.02663427182491065</v>
+        <v>0.01554599359058423</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02663427182491065</v>
+        <v>0.01554599359058423</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005502440620784034</v>
+        <v>0.00538077140702402</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.02756848781825162</v>
+        <v>0.0161262612298258</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02756848781825162</v>
+        <v>0.0161262612298258</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005544091047364376</v>
+        <v>0.005462474185890583</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.02863652090920697</v>
+        <v>0.0167870474436268</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02863652090920697</v>
+        <v>0.0167870474436268</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005647302088381293</v>
+        <v>0.005560569612234879</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.02984033802394961</v>
+        <v>0.0175294159881216</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02984033802394961</v>
+        <v>0.0175294159881216</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005793344629171666</v>
+        <v>0.005675361963126627</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.03118114469800507</v>
+        <v>0.0183538923385637</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03118114469800507</v>
+        <v>0.0183538923385637</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005968469564907884</v>
+        <v>0.005809766667537128</v>
       </c>
     </row>
   </sheetData>
